--- a/KatalonData/IVT/IVT_SameJSON_E2E_SCF.xlsx
+++ b/KatalonData/IVT/IVT_SameJSON_E2E_SCF.xlsx
@@ -8,17 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t470258\Documents\VPS-Katalon\KatalonData\IVT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0038419B-227D-429D-985D-57EA1677A7EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FB21731-36F3-42E6-A91D-3F87D1DD3F82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{A171AD99-6CB3-481A-968B-971B4AF2105E}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="4" activeTab="5" xr2:uid="{A171AD99-6CB3-481A-968B-971B4AF2105E}"/>
   </bookViews>
   <sheets>
     <sheet name="Submit_SameJson_SCF" sheetId="2" r:id="rId1"/>
     <sheet name="CreditCard_SameJson_SCF" sheetId="8" r:id="rId2"/>
-    <sheet name="DebitCard_SameJson" sheetId="13" r:id="rId3"/>
-    <sheet name="PersonalChecking_SameJson" sheetId="10" r:id="rId4"/>
-    <sheet name="PersonalSavings_SameJson" sheetId="14" r:id="rId5"/>
-    <sheet name="BusinessChecking_SameJson" sheetId="12" r:id="rId6"/>
+    <sheet name="DebitCard_SameJson_SCF" sheetId="13" r:id="rId3"/>
+    <sheet name="PersonalChecking_SameJson_SCF" sheetId="10" r:id="rId4"/>
+    <sheet name="PersonalSavings_SameJson_SCF" sheetId="14" r:id="rId5"/>
+    <sheet name="BusinessChecking_SameJson_SCF" sheetId="12" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="62">
   <si>
     <t>Result</t>
   </si>
@@ -157,9 +157,6 @@
     <t>2223520443560010</t>
   </si>
   <si>
-    <t>Tue Sep 15 21:08:53 IST 2026</t>
-  </si>
-  <si>
     <t>RoutingNo</t>
   </si>
   <si>
@@ -199,12 +196,6 @@
     <t>12345</t>
   </si>
   <si>
-    <t>Thu Sep 17 13:26:31 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Sep 17 14:09:28 IST 2026</t>
-  </si>
-  <si>
     <t>BusinessName</t>
   </si>
   <si>
@@ -212,9 +203,6 @@
   </si>
   <si>
     <t>Thu Sep 17 19:48:55 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Sep 29 19:12:49 IST 2026</t>
   </si>
   <si>
     <t>Submit Request:
@@ -262,7 +250,22 @@
 }</t>
   </si>
   <si>
-    <t>Thu Oct 22 19:33:58 IST 2026</t>
+    <t>Fri Oct 23 18:11:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 18:30:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 18:47:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 19:50:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 19:53:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 19:56:32 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -786,7 +789,7 @@
       <c r="A2" s="8"/>
       <c r="B2" s="8"/>
       <c r="C2" s="5" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>4</v>
@@ -795,7 +798,7 @@
         <v>6</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -938,7 +941,7 @@
         <v>8</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>4</v>
@@ -1091,7 +1094,7 @@
         <v>8</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>4</v>
@@ -1171,22 +1174,22 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="I1" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="I1" s="15" t="s">
+      <c r="J1" s="15" t="s">
         <v>42</v>
-      </c>
-      <c r="J1" s="15" t="s">
-        <v>43</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>14</v>
@@ -1248,34 +1251,34 @@
         <v>8</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>4</v>
       </c>
       <c r="E2" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="F2" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="F2" s="4" t="s">
-        <v>46</v>
-      </c>
       <c r="G2" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K2" s="12"/>
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.25">
       <c r="E3" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K3" s="12"/>
     </row>
@@ -1337,22 +1340,22 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="I1" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="I1" s="15" t="s">
+      <c r="J1" s="15" t="s">
         <v>42</v>
-      </c>
-      <c r="J1" s="15" t="s">
-        <v>43</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>14</v>
@@ -1414,34 +1417,34 @@
         <v>8</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>4</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F2" s="16" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G2" s="16" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="K2" s="12"/>
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.25">
       <c r="E3" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F3" s="16" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G3" s="16" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K3" s="12"/>
     </row>
@@ -1503,22 +1506,22 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="I1" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="H1" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="I1" s="15" t="s">
+      <c r="J1" s="15" t="s">
         <v>42</v>
-      </c>
-      <c r="J1" s="15" t="s">
-        <v>43</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>14</v>
@@ -1580,31 +1583,31 @@
         <v>8</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>4</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F2" s="16" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G2" s="16" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="K2" s="12"/>
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.25">
       <c r="E3" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F3" s="16" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="G3" s="16" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="K3" s="12"/>
     </row>
